--- a/04_DESIGN_TABLES/DesignTable_2706_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2706_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN24"/>
+  <dimension ref="A1:AN26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1027,17 +1027,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2706-04-04</t>
+          <t>2706-04-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="C5" t="n">
-        <v>0.39837</v>
+        <v>0.36084</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.625</v>
       </c>
       <c r="E5" t="n">
         <v>0.26092</v>
@@ -1067,22 +1067,22 @@
         <v>0.21647</v>
       </c>
       <c r="N5" t="n">
-        <v>0.21875</v>
+        <v>0.15625</v>
       </c>
       <c r="O5" t="n">
-        <v>0.075</v>
+        <v>0.063</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.852</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.182</v>
+        <v>0.125</v>
       </c>
       <c r="R5" t="n">
-        <v>0.0795</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1135</v>
+        <v>0.1108</v>
       </c>
       <c r="T5" t="n">
         <v>60</v>
@@ -1091,43 +1091,43 @@
         <v>37</v>
       </c>
       <c r="V5" t="n">
-        <v>0.4375</v>
+        <v>0.3125</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="X5" t="n">
-        <v>1.1038</v>
+        <v>1.029</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.02706</v>
+        <v>0.02255</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0125</v>
+        <v>0.01042</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.05</v>
+        <v>0.04167</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.28</v>
+        <v>0.281</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.72</v>
+        <v>0.715</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.17</v>
+        <v>0.062</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.36</v>
+        <v>1.265</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>2706-04-04</t>
+          <t>2706-04-02</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1/4-18 NPTF x 7/16-20 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/4-18 NPTF x 5/16-24 (bulkhead)</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>7/16-20 (bulkhead)</t>
+          <t>5/16-24 (bulkhead)</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1152,19 +1152,24 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1071 Overall Length = 2.080 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1070 "Overall Length" = 1.980 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "L LGTH" = "1.980" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; C2HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1070 "Hex Flat" = 0.625 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "C1 HEX" = "0.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1070 "Side 1 ID" = 0.281 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "A1 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1070 "Side 2 ID" = 0.062 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "B2 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; I1@DRIVE: own Brennan STEP 09_STEP_FILES/BRENNAN_2706-04-02.stp (sha256 d4ff2da4fb37563b...) measured with wave2/straight/scripts/measure_bulkhead.py (validated on Brennan 2705-08-08 = Air-Way I1 1.44): bulkhead tip 1.42 - relief start 0.31 = 1.11; STEP overall 1.98 = OMi / catalog 1.980, hex 0.6251 = 0.625 [Brennan = yes 2026-10-18]; THDMAJ_A@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; OMi Items!U1070 "1/4-18 NPTF"; THDMAJ_B@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; OMi Items!AA1070 "5/16-24 UNF"; $PRP@TubeOD: Brennan TFA p9 TFA-p009-t01 row 2706-04-02 col "TUBE O.D." = "1/8" (= the -02 JIC tube; format of the built 2706 rows); $PRP@Threads: thread texts from the part-number dashes (NPTF[4] / JIC[2]), format of the built 2706 rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L25 / hex / bores from OMi Items (= Brennan TFA p9); I1 measured on the Brennan 2706-04-02 STEP (no Air-Way -02 bulkhead)</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2706-04-04</t>
+          <t>2706-04-02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2706-04-04-LN</t>
+          <t>2706-04-04</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1259,12 +1264,12 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2706-04-04-LN</t>
+          <t>2706-04-04</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1/4-18 NPTF x 7/16-20 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/4-18 NPTF x 7/16-20 (bulkhead)</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -1289,29 +1294,29 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1086 Overall Length = 2.080 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1071 Overall Length = 2.080 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2706-LN-04-04</t>
+          <t>2706-04-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2706-04-06</t>
+          <t>2706-04-04-LN</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="C7" t="n">
-        <v>0.46765</v>
+        <v>0.39837</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E7" t="n">
         <v>0.26092</v>
@@ -1341,22 +1346,22 @@
         <v>0.21647</v>
       </c>
       <c r="N7" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="O7" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9755</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="T7" t="n">
         <v>60</v>
@@ -1365,43 +1370,43 @@
         <v>37</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="W7" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="X7" t="n">
-        <v>1.1735</v>
+        <v>1.1038</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AB7" t="n">
         <v>0.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.281</v>
+        <v>0.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>2706-04-06</t>
+          <t>2706-04-04-LN</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1/4-18 NPTF x 9/16-18 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/4-18 NPTF x 7/16-20 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -1416,7 +1421,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>9/16-18 (bulkhead)</t>
+          <t>7/16-20 (bulkhead)</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -1426,19 +1431,19 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1072 Overall Length = 2.180 (table had 2.19); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1072 Side 2 ID = 0.281 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1086 Overall Length = 2.080 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2706-04-06</t>
+          <t>2706-LN-04-04</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2706-04-06-LN</t>
+          <t>2706-04-06</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1533,12 +1538,12 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2706-04-06-LN</t>
+          <t>2706-04-06</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1/4-18 NPTF x 9/16-18 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/4-18 NPTF x 9/16-18 (bulkhead)</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -1563,19 +1568,19 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1087 Overall Length = 2.180 (table had 2.19); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1087 Side 2 ID = 0.281 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1072 Overall Length = 2.180 (table had 2.19); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1072 Side 2 ID = 0.281 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2706-LN-04-06</t>
+          <t>2706-04-06</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2706-06-06</t>
+          <t>2706-04-06-LN</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1588,31 +1593,31 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="G9" t="n">
         <v>1.7899</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1522</v>
+        <v>0.1582</v>
       </c>
       <c r="I9" t="n">
-        <v>0.65645</v>
+        <v>0.52183</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4078</v>
+        <v>0.4018</v>
       </c>
       <c r="K9" t="n">
         <v>0.05556</v>
       </c>
       <c r="L9" t="n">
-        <v>0.32823</v>
+        <v>0.26092</v>
       </c>
       <c r="M9" t="n">
-        <v>0.28378</v>
+        <v>0.21647</v>
       </c>
       <c r="N9" t="n">
         <v>0.28125</v>
@@ -1657,25 +1662,25 @@
         <v>0.05556</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.41</v>
+        <v>0.28</v>
       </c>
       <c r="AC9" t="n">
         <v>0.73</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.3</v>
+        <v>0.281</v>
       </c>
       <c r="AE9" t="n">
         <v>1.45</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2706-06-06</t>
+          <t>2706-04-06-LN</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 9/16-18 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/4-18 NPTF x 9/16-18 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -1685,7 +1690,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>3/8-18 NPTF</t>
+          <t>1/4-18 NPTF</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1700,19 +1705,19 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1074 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1087 Overall Length = 2.180 (table had 2.19); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1087 Side 2 ID = 0.281 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2706-06-06</t>
+          <t>2706-LN-04-06</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2706-06-06-LN</t>
+          <t>2706-06-06</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1807,12 +1812,12 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2706-06-06-LN</t>
+          <t>2706-06-06</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 9/16-18 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 9/16-18 (bulkhead)</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -1837,29 +1842,29 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1089 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1074 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2706-LN-06-06</t>
+          <t>2706-06-06</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2706-06-08</t>
+          <t>2706-06-06-LN</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="C11" t="n">
-        <v>0.57735</v>
+        <v>0.46765</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E11" t="n">
         <v>0.32823</v>
@@ -1889,22 +1894,22 @@
         <v>0.28378</v>
       </c>
       <c r="N11" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="O11" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="P11" t="n">
-        <v>1.0667</v>
+        <v>0.9755</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="T11" t="n">
         <v>60</v>
@@ -1913,43 +1918,43 @@
         <v>37</v>
       </c>
       <c r="V11" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="X11" t="n">
-        <v>1.3197</v>
+        <v>1.1735</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.391</v>
+        <v>0.41</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.735</v>
+        <v>0.73</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.615</v>
+        <v>1.45</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2706-06-08</t>
+          <t>2706-06-06-LN</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 3/4-16 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 9/16-18 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -1964,7 +1969,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>3/4-16 (bulkhead)</t>
+          <t>9/16-18 (bulkhead)</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -1974,19 +1979,19 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1075 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1075 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1089 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2706-06-08</t>
+          <t>2706-LN-06-06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2706-06-08-LN</t>
+          <t>2706-06-08</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -2081,12 +2086,12 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2706-06-08-LN</t>
+          <t>2706-06-08</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 3/4-16 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 3/4-16 (bulkhead)</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -2111,74 +2116,74 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1090 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1090 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1075 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1075 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2706-LN-06-08</t>
+          <t>2706-06-08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2706-08-06</t>
+          <t>2706-06-08-LN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="C13" t="n">
-        <v>0.50807</v>
+        <v>0.57735</v>
       </c>
       <c r="D13" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="G13" t="n">
         <v>1.7899</v>
       </c>
       <c r="H13" t="n">
-        <v>0.2163</v>
+        <v>0.1522</v>
       </c>
       <c r="I13" t="n">
-        <v>0.81557</v>
+        <v>0.65645</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="K13" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="L13" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="M13" t="n">
-        <v>0.35064</v>
+        <v>0.28378</v>
       </c>
       <c r="N13" t="n">
-        <v>0.28125</v>
+        <v>0.375</v>
       </c>
       <c r="O13" t="n">
-        <v>0.083</v>
+        <v>0.094</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9755</v>
+        <v>1.0667</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2405</v>
+        <v>0.3295</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0898</v>
+        <v>0.0984</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1082</v>
+        <v>0.1546</v>
       </c>
       <c r="T13" t="n">
         <v>60</v>
@@ -2187,43 +2192,43 @@
         <v>37</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5625</v>
+        <v>0.75</v>
       </c>
       <c r="W13" t="n">
-        <v>0.05556</v>
+        <v>0.0625</v>
       </c>
       <c r="X13" t="n">
-        <v>1.1735</v>
+        <v>1.3197</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.03007</v>
+        <v>0.03383</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.01389</v>
+        <v>0.01562</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.05556</v>
+        <v>0.0625</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.53</v>
+        <v>0.391</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.735</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.465</v>
+        <v>1.615</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2706-08-06</t>
+          <t>2706-06-08-LN</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 9/16-18 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 3/4-16 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -2233,12 +2238,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>9/16-18 (bulkhead)</t>
+          <t>3/4-16 (bulkhead)</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -2248,29 +2253,29 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1076 Overall Length = 2.400 (table had 2.34) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1090 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1090 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2706-08-06</t>
+          <t>2706-LN-06-08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2706-08-08-LN</t>
+          <t>2706-08-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="C14" t="n">
-        <v>0.57735</v>
+        <v>0.50807</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="E14" t="n">
         <v>0.40779</v>
@@ -2300,22 +2305,22 @@
         <v>0.35064</v>
       </c>
       <c r="N14" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="O14" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0667</v>
+        <v>0.9755</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="T14" t="n">
         <v>60</v>
@@ -2324,43 +2329,43 @@
         <v>37</v>
       </c>
       <c r="V14" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="X14" t="n">
-        <v>1.3197</v>
+        <v>1.1735</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AB14" t="n">
         <v>0.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.955</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.645</v>
+        <v>1.465</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2706-08-08-LN</t>
+          <t>2706-08-06</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 3/4-16 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 9/16-18 (bulkhead)</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -2375,7 +2380,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3/4-16 (bulkhead)</t>
+          <t>9/16-18 (bulkhead)</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -2385,29 +2390,29 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1092 Overall Length = 2.600 (table had 2.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1076 Overall Length = 2.400 (table had 2.34) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2706-LN-08-08</t>
+          <t>2706-08-06</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2706-08-10</t>
+          <t>2706-08-08-LN</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="C15" t="n">
-        <v>0.65241</v>
+        <v>0.57735</v>
       </c>
       <c r="D15" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
         <v>0.40779</v>
@@ -2437,19 +2442,19 @@
         <v>0.35064</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="O15" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="P15" t="n">
-        <v>1.1773</v>
+        <v>1.0667</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="S15" t="n">
         <v>0.1546</v>
@@ -2461,43 +2466,43 @@
         <v>37</v>
       </c>
       <c r="V15" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="W15" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="X15" t="n">
-        <v>1.4433</v>
+        <v>1.3197</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.484</v>
+        <v>0.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.985</v>
+        <v>0.955</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.815</v>
+        <v>1.645</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2706-08-10</t>
+          <t>2706-08-08-LN</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 7/8-14 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 3/4-16 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -2512,7 +2517,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>7/8-14 (bulkhead)</t>
+          <t>3/4-16 (bulkhead)</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -2522,19 +2527,19 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1078 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1078 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1092 Overall Length = 2.600 (table had 2.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2706-08-10</t>
+          <t>2706-LN-08-08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2706-08-10-LN</t>
+          <t>2706-08-10</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -2629,12 +2634,12 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2706-08-10-LN</t>
+          <t>2706-08-10</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 7/8-14 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 7/8-14 (bulkhead)</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -2659,74 +2664,74 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1093 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1093 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1078 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1078 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2706-LN-08-10</t>
+          <t>2706-08-10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2706-12-12</t>
+          <t>2706-08-10-LN</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="C17" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D17" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E17" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="G17" t="n">
         <v>1.7899</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2043</v>
+        <v>0.2163</v>
       </c>
       <c r="I17" t="n">
-        <v>1.02482</v>
+        <v>0.81557</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="K17" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="M17" t="n">
-        <v>0.45527</v>
+        <v>0.35064</v>
       </c>
       <c r="N17" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="O17" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="P17" t="n">
-        <v>1.2755</v>
+        <v>1.1773</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="T17" t="n">
         <v>60</v>
@@ -2735,43 +2740,43 @@
         <v>37</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="W17" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>1.5905</v>
+        <v>1.4433</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.72</v>
+        <v>0.484</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.96</v>
+        <v>0.985</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.96</v>
+        <v>1.815</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2706-12-12</t>
+          <t>2706-08-10-LN</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 3/4-14 NPTF x 1 1/16-12 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 7/8-14 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -2781,12 +2786,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1 1/16-12 (bulkhead)</t>
+          <t>7/8-14 (bulkhead)</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -2796,19 +2801,19 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1093 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1093 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2706-12-12</t>
+          <t>2706-LN-08-10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2706-12-12-LN</t>
+          <t>2706-12-12</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -2903,12 +2908,12 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2706-12-12-LN</t>
+          <t>2706-12-12</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 3/4-14 NPTF x 1 1/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 3/4-14 NPTF x 1 1/16-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -2928,7 +2933,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -2936,56 +2941,61 @@
           <t>Air-Way s74 only (double-pass 25 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L25@DRIVE=2.92~2.920; C2HEX@HEX=1.38~1.375; D1@BORE=0.72~0.719; D@BORE=0.61~0.609</t>
+        </is>
+      </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2706-LN-12-12</t>
+          <t>2706-12-12</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2706-16-16</t>
+          <t>2706-12-12-LN</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.17</v>
+        <v>2.92</v>
       </c>
       <c r="C19" t="n">
-        <v>0.94108</v>
+        <v>0.79674</v>
       </c>
       <c r="D19" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="G19" t="n">
         <v>1.7899</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2572</v>
+        <v>0.2043</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2832</v>
+        <v>1.02482</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="K19" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="M19" t="n">
-        <v>0.57203</v>
+        <v>0.45527</v>
       </c>
       <c r="N19" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="O19" t="n">
         <v>0.125</v>
@@ -2994,13 +3004,13 @@
         <v>1.2755</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="T19" t="n">
         <v>60</v>
@@ -3009,7 +3019,7 @@
         <v>37</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="W19" t="n">
         <v>0.08333</v>
@@ -3027,25 +3037,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.18</v>
+        <v>0.96</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2706-16-16</t>
+          <t>2706-12-12-LN</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1-11 1/2 NPTF x 1 5/16-12 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 3/4-14 NPTF x 1 1/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -3055,34 +3065,39 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1 5/16-12 (bulkhead)</t>
+          <t>1 1/16-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1080 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L25@DRIVE=2.92~2.920; C2HEX@HEX=1.38~1.375; D1@BORE=0.72~0.719; D@BORE=0.61~0.609</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2706-16-16</t>
+          <t>2706-LN-12-12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2706-16-16-LN</t>
+          <t>2706-16-16</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -3177,12 +3192,12 @@
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2706-16-16-LN</t>
+          <t>2706-16-16</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1-11 1/2 NPTF x 1 5/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1-11 1/2 NPTF x 1 5/16-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -3207,74 +3222,74 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1095 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1080 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2706-LN-16-16</t>
+          <t>2706-16-16</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2706-20-20</t>
+          <t>2706-16-16-LN</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.32</v>
+        <v>3.17</v>
       </c>
       <c r="C21" t="n">
-        <v>1.08542</v>
+        <v>0.94108</v>
       </c>
       <c r="D21" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="E21" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="G21" t="n">
         <v>1.7899</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2632</v>
+        <v>0.2572</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6267</v>
+        <v>1.2832</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="K21" t="n">
         <v>0.08696</v>
       </c>
       <c r="L21" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>0.74378</v>
+        <v>0.57203</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="O21" t="n">
         <v>0.125</v>
       </c>
       <c r="P21" t="n">
-        <v>1.2736</v>
+        <v>1.2755</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="R21" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="T21" t="n">
         <v>60</v>
@@ -3283,13 +3298,13 @@
         <v>37</v>
       </c>
       <c r="V21" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="W21" t="n">
         <v>0.08333</v>
       </c>
       <c r="X21" t="n">
-        <v>1.6406</v>
+        <v>1.5905</v>
       </c>
       <c r="Y21" t="n">
         <v>0.04511</v>
@@ -3301,25 +3316,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.245</v>
+        <v>1.18</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AE21" t="n">
-        <v>2.075</v>
+        <v>1.99</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2706-20-20</t>
+          <t>2706-16-16-LN</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1 1/4-11 1/2 NPTF x 1 5/8-12 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1-11 1/2 NPTF x 1 5/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -3329,12 +3344,12 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>1 5/8-12 (bulkhead)</t>
+          <t>1 5/16-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -3344,19 +3359,19 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1081 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1095 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2706-20-20</t>
+          <t>2706-LN-16-16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2706-20-20-LN</t>
+          <t>2706-20-20</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -3451,12 +3466,12 @@
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2706-20-20-LN</t>
+          <t>2706-20-20</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1 1/4-11 1/2 NPTF x 1 5/8-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1 1/4-11 1/2 NPTF x 1 5/8-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -3481,74 +3496,74 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1096 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1081 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2706-LN-20-20</t>
+          <t>2706-20-20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2706-24-24</t>
+          <t>2706-20-20-LN</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="C23" t="n">
-        <v>1.22976</v>
+        <v>1.08542</v>
       </c>
       <c r="D23" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="E23" t="n">
-        <v>0.93283</v>
+        <v>0.81335</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7235</v>
+        <v>0.7068</v>
       </c>
       <c r="G23" t="n">
         <v>1.7899</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2765</v>
+        <v>0.2632</v>
       </c>
       <c r="I23" t="n">
-        <v>1.86566</v>
+        <v>1.6267</v>
       </c>
       <c r="J23" t="n">
-        <v>0.7235</v>
+        <v>0.7068</v>
       </c>
       <c r="K23" t="n">
         <v>0.08696</v>
       </c>
       <c r="L23" t="n">
-        <v>0.93283</v>
+        <v>0.81335</v>
       </c>
       <c r="M23" t="n">
-        <v>0.86326</v>
+        <v>0.74378</v>
       </c>
       <c r="N23" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="O23" t="n">
         <v>0.125</v>
       </c>
       <c r="P23" t="n">
-        <v>1.2724</v>
+        <v>1.2736</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="T23" t="n">
         <v>60</v>
@@ -3557,13 +3572,13 @@
         <v>37</v>
       </c>
       <c r="V23" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="W23" t="n">
         <v>0.08333</v>
       </c>
       <c r="X23" t="n">
-        <v>1.6504</v>
+        <v>1.6406</v>
       </c>
       <c r="Y23" t="n">
         <v>0.04511</v>
@@ -3575,25 +3590,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.312</v>
+        <v>1.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.345</v>
+        <v>1.245</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.155</v>
+        <v>2.075</v>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2706-24-24</t>
+          <t>2706-20-20-LN</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1 1/2-11 1/2 NPTF x 1 7/8-12 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1 1/4-11 1/2 NPTF x 1 5/8-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -3603,12 +3618,12 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>1 7/8-12 (bulkhead)</t>
+          <t>1 5/8-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -3618,19 +3633,19 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1082 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1082 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1096 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2706-24-24</t>
+          <t>2706-LN-20-20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2706-24-24-LN</t>
+          <t>2706-24-24</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -3725,47 +3740,326 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
+          <t>2706-24-24</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Male Pipe x JIC Bulkhead Connector, 1 1/2-11 1/2 NPTF x 1 7/8-12 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1082 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1082 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>2706-24-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>2706-24-24-LN</t>
         </is>
       </c>
-      <c r="AG24" t="inlineStr">
+      <c r="B25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.22976</v>
+      </c>
+      <c r="D25" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.86566</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.7235</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.93283</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.86326</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.2724</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.8774999999999999</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.1298</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="T25" t="n">
+        <v>60</v>
+      </c>
+      <c r="U25" t="n">
+        <v>37</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.6504</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.345</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.155</v>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>2706-24-24-LN</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
         <is>
           <t>Male Pipe x JIC Bulkhead Connector, 1 1/2-11 1/2 NPTF x 1 7/8-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
-      <c r="AH24" t="inlineStr">
+      <c r="AH25" t="inlineStr">
         <is>
           <t>2706</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
+      <c r="AI25" t="inlineStr">
         <is>
           <t>1 1/2-11 1/2 NPTF</t>
         </is>
       </c>
-      <c r="AJ24" t="inlineStr">
+      <c r="AJ25" t="inlineStr">
         <is>
           <t>1 7/8-12 (bulkhead)</t>
         </is>
       </c>
-      <c r="AK24" t="inlineStr">
+      <c r="AK25" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AL24" t="inlineStr">
+      <c r="AL25" t="inlineStr">
         <is>
           <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1097 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1097 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; THDMAJ_A@DRIVE: 1.900 = ASME B1.20.1 1-1/2 NPT OD (ms51500.NPTF[24]) for the part-number dash -24 (table had empty: Air-Way callout "1 1/2-11" = nominal 1 1/2 with a TPI misprint); OMi Items!U1097 "1 1/2-11 1/2 NPFT" and Brennan TFA p9 "1-1/2-11-1/2" agree [thread size from the OMi dimension file's own thread cell Items!U1097 (OMi first, user 2026-09-25), not a dash transfer; Q18 / Q-THREAD not needed (impact F45D) - single source, ASSUMED] [batch 15 2026-10-02, staged] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
+      <c r="AM25" t="inlineStr">
         <is>
           <t>A NPTF printed "1 1/2-11" on Air-Way (sibling 1 1/2-11 1/2); copied as printed in $PRP@Threads - as-printed, likely typo | RESOLVED 2026-10-02 (batch 15, staged): THDMAJ_A = 1.900, the 1-1/2 NPT of the part-number dash -24 (ASME B1.20.1); OMi Items!U1097 prints "1 1/2-11 1/2 NPFT" and Brennan TFA p9 2706-24-24 prints "1-1/2-11-1/2"; the OMi thread cell is the source (no dash transfer, Q-THREAD not needed per impact F45D) - ASSUMED</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
+      <c r="AN25" t="inlineStr">
         <is>
           <t>2706-LN-24-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2706-LN-04-02</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="T26" t="n">
+        <v>60</v>
+      </c>
+      <c r="U26" t="n">
+        <v>37</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.04167</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.029</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.02255</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.01042</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.04167</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>2706-LN-04-02</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/4-18 NPTF x 5/16-24 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>1/4-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>5/16-24 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1085 "Overall Length" = 1.980 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "L LGTH" = "1.980" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; C2HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1085 "Hex Flat" = 0.625 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "C1 HEX" = "0.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1085 "Side 1 ID" = 0.281 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "A1 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1085 "Side 2 ID" = 0.062 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "B2 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; I1@DRIVE: own Brennan STEP 09_STEP_FILES/BRENNAN_2706-04-02.stp (sha256 d4ff2da4fb37563b...) measured with wave2/straight/scripts/measure_bulkhead.py (validated on Brennan 2705-08-08 = Air-Way I1 1.44): bulkhead tip 1.42 - relief start 0.31 = 1.11; STEP overall 1.98 = OMi / catalog 1.980, hex 0.6251 = 0.625 [Brennan = yes 2026-10-18] [the -LN part = the plain 2706-04-02 + a locknut: Q-TRANSFER-LN open]; THDMAJ_A@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; OMi Items!U1085 "1/4-18 NPTF"; THDMAJ_B@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; OMi Items!AA1085 "5/16-24 UNF"; $PRP@TubeOD: Brennan TFA p9 TFA-p009-t01 row 2706-04-02 col "TUBE O.D." = "1/8" (= the -02 JIC tube; format of the built 2706 rows); $PRP@Threads: thread texts from the part-number dashes (NPTF[4] / JIC[2]), format of the built 2706 rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L25 / hex / bores from OMi Items (= Brennan TFA p9); I1 measured on the Brennan 2706-04-02 STEP (no Air-Way -02 bulkhead) - copied from the plain part (Q-TRANSFER-LN)</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>2706-LN-04-02</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_2706_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2706_SW2.xlsx
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="C2" t="n">
         <v>0.57735</v>
@@ -701,13 +701,13 @@
         <v>0.53</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.955</v>
+        <v>0.92</v>
       </c>
       <c r="AD2" t="n">
         <v>0.39</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.645</v>
+        <v>1.61</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -741,7 +741,12 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1077 Overall Length = 2.600 (table had 2.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1077 Overall Length = 2.600 (table had 2.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.6) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.6 -&gt; Air-Way 2.53</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -835,7 +840,7 @@
         <v>0.05</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.172</v>
+        <v>0.19</v>
       </c>
       <c r="AC3" t="n">
         <v>0.51</v>
@@ -878,7 +883,12 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1069 Side 1 ID = 0.172 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1069 Side 1 ID = 0.172 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: Air-Way 0.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.172) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.172 -&gt; Air-Way 0.19</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
@@ -972,7 +982,7 @@
         <v>0.05</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.172</v>
+        <v>0.19</v>
       </c>
       <c r="AC4" t="n">
         <v>0.51</v>
@@ -1015,7 +1025,12 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1084 Side 1 ID = 0.172 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1084 Side 1 ID = 0.172 (table had 0.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: Air-Way 0.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.172) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.172 -&gt; Air-Way 0.19</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
@@ -1173,7 +1188,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="C6" t="n">
         <v>0.39837</v>
@@ -1254,13 +1269,13 @@
         <v>0.28</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.72</v>
+        <v>0.695</v>
       </c>
       <c r="AD6" t="n">
         <v>0.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.36</v>
+        <v>1.335</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1294,7 +1309,12 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1071 Overall Length = 2.080 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1071 Overall Length = 2.080 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.03 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.08) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.08 -&gt; Air-Way 2.03</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -1310,7 +1330,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="C7" t="n">
         <v>0.39837</v>
@@ -1391,13 +1411,13 @@
         <v>0.28</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.72</v>
+        <v>0.695</v>
       </c>
       <c r="AD7" t="n">
         <v>0.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.36</v>
+        <v>1.335</v>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
@@ -1431,7 +1451,12 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1086 Overall Length = 2.080 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1086 Overall Length = 2.080 (table had 2.03) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.03 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.08) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.08 -&gt; Air-Way 2.03</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
@@ -1447,7 +1472,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="C8" t="n">
         <v>0.46765</v>
@@ -1528,13 +1553,13 @@
         <v>0.28</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.73</v>
+        <v>0.735</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.281</v>
+        <v>0.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.45</v>
+        <v>1.455</v>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
@@ -1568,7 +1593,12 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1072 Overall Length = 2.180 (table had 2.19); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1072 Side 2 ID = 0.281 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1072 Overall Length = 2.180 (table had 2.19); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1072 Side 2 ID = 0.281 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D@BORE: Air-Way 0.3 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.281) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.18 -&gt; Air-Way 2.19 | 2026-10-20 Air-Way first: D@BORE OMi/Brennan 0.281 -&gt; Air-Way 0.3</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
@@ -1584,7 +1614,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="C9" t="n">
         <v>0.46765</v>
@@ -1665,13 +1695,13 @@
         <v>0.28</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.73</v>
+        <v>0.735</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.281</v>
+        <v>0.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.45</v>
+        <v>1.455</v>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
@@ -1705,7 +1735,12 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1087 Overall Length = 2.180 (table had 2.19); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1087 Side 2 ID = 0.281 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1087 Overall Length = 2.180 (table had 2.19); D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1087 Side 2 ID = 0.281 (table had 0.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D@BORE: Air-Way 0.3 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.281) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.18 -&gt; Air-Way 2.19 | 2026-10-20 Air-Way first: D@BORE OMi/Brennan 0.281 -&gt; Air-Way 0.3</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
@@ -1721,7 +1756,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="C10" t="n">
         <v>0.46765</v>
@@ -1802,13 +1837,13 @@
         <v>0.41</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.73</v>
+        <v>0.735</v>
       </c>
       <c r="AD10" t="n">
         <v>0.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.45</v>
+        <v>1.455</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
@@ -1842,7 +1877,12 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1074 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1074 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.18 -&gt; Air-Way 2.19</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
@@ -1858,7 +1898,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="C11" t="n">
         <v>0.46765</v>
@@ -1939,13 +1979,13 @@
         <v>0.41</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.73</v>
+        <v>0.735</v>
       </c>
       <c r="AD11" t="n">
         <v>0.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.45</v>
+        <v>1.455</v>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
@@ -1979,7 +2019,12 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1089 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1089 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.18 -&gt; Air-Way 2.19</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
@@ -1995,7 +2040,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="C12" t="n">
         <v>0.57735</v>
@@ -2073,16 +2118,16 @@
         <v>0.0625</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.391</v>
+        <v>0.41</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.735</v>
+        <v>0.74</v>
       </c>
       <c r="AD12" t="n">
         <v>0.39</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.615</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
@@ -2116,7 +2161,12 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1075 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1075 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1075 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1075 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.36 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.35) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.41 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.391) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.35 -&gt; Air-Way 2.36 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.391 -&gt; Air-Way 0.41</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
@@ -2132,7 +2182,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="C13" t="n">
         <v>0.57735</v>
@@ -2210,16 +2260,16 @@
         <v>0.0625</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.391</v>
+        <v>0.41</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.735</v>
+        <v>0.74</v>
       </c>
       <c r="AD13" t="n">
         <v>0.39</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.615</v>
+        <v>1.62</v>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
@@ -2253,7 +2303,12 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1090 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1090 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1090 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1090 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.36 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.35) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.41 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.391) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.35 -&gt; Air-Way 2.36 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.391 -&gt; Air-Way 0.41</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
@@ -2269,7 +2324,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="C14" t="n">
         <v>0.50807</v>
@@ -2350,13 +2405,13 @@
         <v>0.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.905</v>
       </c>
       <c r="AD14" t="n">
         <v>0.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.465</v>
+        <v>1.435</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
@@ -2390,7 +2445,12 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1076 Overall Length = 2.400 (table had 2.34) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1076 Overall Length = 2.400 (table had 2.34) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.4) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.4 -&gt; Air-Way 2.34</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
@@ -2406,7 +2466,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="C15" t="n">
         <v>0.57735</v>
@@ -2487,13 +2547,13 @@
         <v>0.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.955</v>
+        <v>0.92</v>
       </c>
       <c r="AD15" t="n">
         <v>0.39</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.645</v>
+        <v>1.61</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
@@ -2527,7 +2587,12 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1092 Overall Length = 2.600 (table had 2.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1092 Overall Length = 2.600 (table had 2.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.6) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.6 -&gt; Air-Way 2.53</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
@@ -2543,7 +2608,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="C16" t="n">
         <v>0.65241</v>
@@ -2621,16 +2686,16 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.484</v>
+        <v>0.53</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.985</v>
+        <v>0.945</v>
       </c>
       <c r="AD16" t="n">
         <v>0.48</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.815</v>
+        <v>1.775</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
@@ -2664,7 +2729,12 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1078 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1078 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1078 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1078 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.8) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.484) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.8 -&gt; Air-Way 2.72 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.484 -&gt; Air-Way 0.53</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
@@ -2680,7 +2750,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="C17" t="n">
         <v>0.65241</v>
@@ -2758,16 +2828,16 @@
         <v>0.07142999999999999</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.484</v>
+        <v>0.53</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.985</v>
+        <v>0.945</v>
       </c>
       <c r="AD17" t="n">
         <v>0.48</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.815</v>
+        <v>1.775</v>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
@@ -2801,7 +2871,12 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1093 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1093 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1093 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1093 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.8) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.484) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.8 -&gt; Air-Way 2.72 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.484 -&gt; Air-Way 0.53</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
@@ -3101,7 +3176,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="C20" t="n">
         <v>0.94108</v>
@@ -3182,13 +3257,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AD20" t="n">
         <v>0.84</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
@@ -3222,7 +3297,12 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1080 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1080 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.17 -&gt; Air-Way 3.11</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
@@ -3238,7 +3318,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="C21" t="n">
         <v>0.94108</v>
@@ -3319,13 +3399,13 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AD21" t="n">
         <v>0.84</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
@@ -3359,7 +3439,12 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1095 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1095 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.17 -&gt; Air-Way 3.11</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
@@ -3375,7 +3460,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="C22" t="n">
         <v>1.08542</v>
@@ -3456,13 +3541,13 @@
         <v>1.25</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.245</v>
+        <v>1.21</v>
       </c>
       <c r="AD22" t="n">
         <v>1.08</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.075</v>
+        <v>2.04</v>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
@@ -3496,7 +3581,12 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1081 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1081 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.32) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.32 -&gt; Air-Way 3.25</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
@@ -3512,7 +3602,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="C23" t="n">
         <v>1.08542</v>
@@ -3593,13 +3683,13 @@
         <v>1.25</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.245</v>
+        <v>1.21</v>
       </c>
       <c r="AD23" t="n">
         <v>1.08</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.075</v>
+        <v>2.04</v>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
@@ -3633,7 +3723,12 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1096 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1096 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.32) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.32 -&gt; Air-Way 3.25</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
@@ -3649,7 +3744,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="C24" t="n">
         <v>1.22976</v>
@@ -3727,16 +3822,16 @@
         <v>0.08333</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.312</v>
+        <v>1.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.345</v>
+        <v>1.315</v>
       </c>
       <c r="AD24" t="n">
         <v>1.31</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.155</v>
+        <v>2.125</v>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
@@ -3770,7 +3865,12 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1082 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1082 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1082 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1082 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.44 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 1.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.312) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.5 -&gt; Air-Way 3.44 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 1.312 -&gt; Air-Way 1.5</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
@@ -3786,7 +3886,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="C25" t="n">
         <v>1.22976</v>
@@ -3864,16 +3964,16 @@
         <v>0.08333</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.312</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.345</v>
+        <v>1.315</v>
       </c>
       <c r="AD25" t="n">
         <v>1.31</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.155</v>
+        <v>2.125</v>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
@@ -3907,12 +4007,12 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1097 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1097 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; THDMAJ_A@DRIVE: 1.900 = ASME B1.20.1 1-1/2 NPT OD (ms51500.NPTF[24]) for the part-number dash -24 (table had empty: Air-Way callout "1 1/2-11" = nominal 1 1/2 with a TPI misprint); OMi Items!U1097 "1 1/2-11 1/2 NPFT" and Brennan TFA p9 "1-1/2-11-1/2" agree [thread size from the OMi dimension file's own thread cell Items!U1097 (OMi first, user 2026-09-25), not a dash transfer; Q18 / Q-THREAD not needed (impact F45D) - single source, ASSUMED] [batch 15 2026-10-02, staged] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1097 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1097 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; THDMAJ_A@DRIVE: 1.900 = ASME B1.20.1 1-1/2 NPT OD (ms51500.NPTF[24]) for the part-number dash -24 (table had empty: Air-Way callout "1 1/2-11" = nominal 1 1/2 with a TPI misprint); OMi Items!U1097 "1 1/2-11 1/2 NPFT" and Brennan TFA p9 "1-1/2-11-1/2" agree [thread size from the OMi dimension file's own thread cell Items!U1097 (OMi first, user 2026-09-25), not a dash transfer; Q18 / Q-THREAD not needed (impact F45D) - single source, ASSUMED] [batch 15 2026-10-02, staged]; L25@DRIVE: Air-Way 3.44 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 1.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.312) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>A NPTF printed "1 1/2-11" on Air-Way (sibling 1 1/2-11 1/2); copied as printed in $PRP@Threads - as-printed, likely typo | RESOLVED 2026-10-02 (batch 15, staged): THDMAJ_A = 1.900, the 1-1/2 NPT of the part-number dash -24 (ASME B1.20.1); OMi Items!U1097 prints "1 1/2-11 1/2 NPFT" and Brennan TFA p9 2706-24-24 prints "1-1/2-11-1/2"; the OMi thread cell is the source (no dash transfer, Q-THREAD not needed per impact F45D) - ASSUMED</t>
+          <t>A NPTF printed "1 1/2-11" on Air-Way (sibling 1 1/2-11 1/2); copied as printed in $PRP@Threads - as-printed, likely typo | RESOLVED 2026-10-02 (batch 15, staged): THDMAJ_A = 1.900, the 1-1/2 NPT of the part-number dash -24 (ASME B1.20.1); OMi Items!U1097 prints "1 1/2-11 1/2 NPFT" and Brennan TFA p9 2706-24-24 prints "1-1/2-11-1/2"; the OMi thread cell is the source (no dash transfer, Q-THREAD not needed per impact F45D) - ASSUMED | 2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.5 -&gt; Air-Way 3.44 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 1.312 -&gt; Air-Way 1.5</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">

--- a/04_DESIGN_TABLES/DesignTable_2706_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2706_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN26"/>
+  <dimension ref="A1:AN30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,17 +1752,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2706-06-06</t>
+          <t>2706-06-04</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2.19</v>
       </c>
       <c r="C10" t="n">
-        <v>0.46765</v>
+        <v>0.43301</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="E10" t="n">
         <v>0.32823</v>
@@ -1792,22 +1792,22 @@
         <v>0.28378</v>
       </c>
       <c r="N10" t="n">
-        <v>0.28125</v>
+        <v>0.21875</v>
       </c>
       <c r="O10" t="n">
-        <v>0.083</v>
+        <v>0.075</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9755</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2405</v>
+        <v>0.182</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0898</v>
+        <v>0.0795</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1082</v>
+        <v>0.1135</v>
       </c>
       <c r="T10" t="n">
         <v>60</v>
@@ -1816,43 +1816,43 @@
         <v>37</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5625</v>
+        <v>0.4375</v>
       </c>
       <c r="W10" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1735</v>
+        <v>1.1038</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.03007</v>
+        <v>0.02706</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.01389</v>
+        <v>0.0125</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.05556</v>
+        <v>0.05</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.41</v>
+        <v>0.406</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.735</v>
+        <v>0.775</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.3</v>
+        <v>0.172</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.455</v>
+        <v>1.415</v>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2706-06-06</t>
+          <t>2706-06-04</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 9/16-18 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 7/16-20 (bulkhead)</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -1867,7 +1867,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>9/16-18 (bulkhead)</t>
+          <t>7/16-20 (bulkhead)</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -1877,24 +1877,24 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1074 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L25 / hex / D1 / D = OMi WebsitePartsInfo2026.xlsx Items row 1073; I1 1.20 = Air-Way -04 bulkhead (A8); thread majors from the end library; not printed in the Brennan TFA catalog | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.18 -&gt; Air-Way 2.19</t>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 1073 + A8 I1 per size; not printed in the Brennan TFA catalog</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2706-06-06</t>
+          <t>2706-06-04</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2706-06-06-LN</t>
+          <t>2706-06-06</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1989,12 +1989,12 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2706-06-06-LN</t>
+          <t>2706-06-06</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 9/16-18 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 9/16-18 (bulkhead)</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1089 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1074 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -2029,24 +2029,24 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2706-LN-06-06</t>
+          <t>2706-06-06</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2706-06-08</t>
+          <t>2706-06-06-LN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="C12" t="n">
-        <v>0.57735</v>
+        <v>0.46765</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E12" t="n">
         <v>0.32823</v>
@@ -2076,22 +2076,22 @@
         <v>0.28378</v>
       </c>
       <c r="N12" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="O12" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="P12" t="n">
-        <v>1.0667</v>
+        <v>0.9755</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="R12" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="T12" t="n">
         <v>60</v>
@@ -2100,43 +2100,43 @@
         <v>37</v>
       </c>
       <c r="V12" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="X12" t="n">
-        <v>1.3197</v>
+        <v>1.1735</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AB12" t="n">
         <v>0.41</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.74</v>
+        <v>0.735</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>1.455</v>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2706-06-08</t>
+          <t>2706-06-06-LN</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 3/4-16 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 9/16-18 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>3/4-16 (bulkhead)</t>
+          <t>9/16-18 (bulkhead)</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1075 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1075 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.36 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.35) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.41 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.391) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1089 Overall Length = 2.180 (table had 2.19) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.19 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.18) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.35 -&gt; Air-Way 2.36 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.391 -&gt; Air-Way 0.41</t>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.18 -&gt; Air-Way 2.19</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2706-06-08</t>
+          <t>2706-LN-06-06</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2706-06-08-LN</t>
+          <t>2706-06-08</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2706-06-08-LN</t>
+          <t>2706-06-08</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 3/4-16 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 3/4-16 (bulkhead)</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1090 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1090 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.36 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.35) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.41 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.391) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1075 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1075 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.36 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.35) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.41 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.391) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -2313,69 +2313,69 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2706-LN-06-08</t>
+          <t>2706-06-08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2706-08-06</t>
+          <t>2706-06-08-LN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="C14" t="n">
-        <v>0.50807</v>
+        <v>0.57735</v>
       </c>
       <c r="D14" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="G14" t="n">
         <v>1.7899</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2163</v>
+        <v>0.1522</v>
       </c>
       <c r="I14" t="n">
-        <v>0.81557</v>
+        <v>0.65645</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5337</v>
+        <v>0.4078</v>
       </c>
       <c r="K14" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="L14" t="n">
-        <v>0.40779</v>
+        <v>0.32823</v>
       </c>
       <c r="M14" t="n">
-        <v>0.35064</v>
+        <v>0.28378</v>
       </c>
       <c r="N14" t="n">
-        <v>0.28125</v>
+        <v>0.375</v>
       </c>
       <c r="O14" t="n">
-        <v>0.083</v>
+        <v>0.094</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9755</v>
+        <v>1.0667</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.2405</v>
+        <v>0.3295</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0898</v>
+        <v>0.0984</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1082</v>
+        <v>0.1546</v>
       </c>
       <c r="T14" t="n">
         <v>60</v>
@@ -2384,43 +2384,43 @@
         <v>37</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5625</v>
+        <v>0.75</v>
       </c>
       <c r="W14" t="n">
-        <v>0.05556</v>
+        <v>0.0625</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1735</v>
+        <v>1.3197</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.03007</v>
+        <v>0.03383</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.01389</v>
+        <v>0.01562</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.05556</v>
+        <v>0.0625</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.53</v>
+        <v>0.41</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.905</v>
+        <v>0.74</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.435</v>
+        <v>1.62</v>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2706-08-06</t>
+          <t>2706-06-08-LN</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 9/16-18 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 3/4-16 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>1/2-14 NPTF</t>
+          <t>3/8-18 NPTF</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>9/16-18 (bulkhead)</t>
+          <t>3/4-16 (bulkhead)</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
@@ -2445,34 +2445,34 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1076 Overall Length = 2.400 (table had 2.34) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.4) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1090 Overall Length = 2.350 (table had 2.36); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1090 Side 1 ID = 0.391 (table had 0.41) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.36 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.35) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.41 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.391) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.4 -&gt; Air-Way 2.34</t>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.35 -&gt; Air-Way 2.36 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.391 -&gt; Air-Way 0.41</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2706-08-06</t>
+          <t>2706-LN-06-08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2706-08-08-LN</t>
+          <t>2706-08-06</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="C15" t="n">
-        <v>0.57735</v>
+        <v>0.50807</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="E15" t="n">
         <v>0.40779</v>
@@ -2502,22 +2502,22 @@
         <v>0.35064</v>
       </c>
       <c r="N15" t="n">
-        <v>0.375</v>
+        <v>0.28125</v>
       </c>
       <c r="O15" t="n">
-        <v>0.094</v>
+        <v>0.083</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0667</v>
+        <v>0.9755</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3295</v>
+        <v>0.2405</v>
       </c>
       <c r="R15" t="n">
-        <v>0.0984</v>
+        <v>0.0898</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1546</v>
+        <v>0.1082</v>
       </c>
       <c r="T15" t="n">
         <v>60</v>
@@ -2526,43 +2526,43 @@
         <v>37</v>
       </c>
       <c r="V15" t="n">
-        <v>0.75</v>
+        <v>0.5625</v>
       </c>
       <c r="W15" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="X15" t="n">
-        <v>1.3197</v>
+        <v>1.1735</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.03383</v>
+        <v>0.03007</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.01562</v>
+        <v>0.01389</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.0625</v>
+        <v>0.05556</v>
       </c>
       <c r="AB15" t="n">
         <v>0.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.92</v>
+        <v>0.905</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.39</v>
+        <v>0.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.61</v>
+        <v>1.435</v>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2706-08-08-LN</t>
+          <t>2706-08-06</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 3/4-16 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 9/16-18 (bulkhead)</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3/4-16 (bulkhead)</t>
+          <t>9/16-18 (bulkhead)</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -2587,34 +2587,34 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1092 Overall Length = 2.600 (table had 2.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.6) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1076 Overall Length = 2.400 (table had 2.34) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.34 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.4) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.6 -&gt; Air-Way 2.53</t>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.4 -&gt; Air-Way 2.34</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2706-LN-08-08</t>
+          <t>2706-08-06</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2706-08-10</t>
+          <t>2706-08-08-LN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="C16" t="n">
-        <v>0.65241</v>
+        <v>0.57735</v>
       </c>
       <c r="D16" t="n">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>0.40779</v>
@@ -2644,19 +2644,19 @@
         <v>0.35064</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4375</v>
+        <v>0.375</v>
       </c>
       <c r="O16" t="n">
-        <v>0.107</v>
+        <v>0.094</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1773</v>
+        <v>1.0667</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.386</v>
+        <v>0.3295</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1114</v>
+        <v>0.0984</v>
       </c>
       <c r="S16" t="n">
         <v>0.1546</v>
@@ -2668,43 +2668,43 @@
         <v>37</v>
       </c>
       <c r="V16" t="n">
-        <v>0.875</v>
+        <v>0.75</v>
       </c>
       <c r="W16" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="X16" t="n">
-        <v>1.4433</v>
+        <v>1.3197</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.03866</v>
+        <v>0.03383</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.01786</v>
+        <v>0.01562</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="AB16" t="n">
         <v>0.53</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.945</v>
+        <v>0.92</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.48</v>
+        <v>0.39</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.775</v>
+        <v>1.61</v>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2706-08-10</t>
+          <t>2706-08-08-LN</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 7/8-14 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 3/4-16 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>7/8-14 (bulkhead)</t>
+          <t>3/4-16 (bulkhead)</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -2729,24 +2729,24 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1078 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1078 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.8) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.484) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1092 Overall Length = 2.600 (table had 2.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.6) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.8 -&gt; Air-Way 2.72 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.484 -&gt; Air-Way 0.53</t>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.6 -&gt; Air-Way 2.53</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2706-08-10</t>
+          <t>2706-LN-08-08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2706-08-10-LN</t>
+          <t>2706-08-10</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2706-08-10-LN</t>
+          <t>2706-08-10</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 7/8-14 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 7/8-14 (bulkhead)</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1093 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1093 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.8) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.484) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1078 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1078 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.8) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.484) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -2881,69 +2881,69 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2706-LN-08-10</t>
+          <t>2706-08-10</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2706-12-12</t>
+          <t>2706-08-10-LN</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="C18" t="n">
-        <v>0.79674</v>
+        <v>0.65241</v>
       </c>
       <c r="D18" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="E18" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="G18" t="n">
         <v>1.7899</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2043</v>
+        <v>0.2163</v>
       </c>
       <c r="I18" t="n">
-        <v>1.02482</v>
+        <v>0.81557</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5457</v>
+        <v>0.5337</v>
       </c>
       <c r="K18" t="n">
         <v>0.07142999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>0.51241</v>
+        <v>0.40779</v>
       </c>
       <c r="M18" t="n">
-        <v>0.45527</v>
+        <v>0.35064</v>
       </c>
       <c r="N18" t="n">
-        <v>0.53125</v>
+        <v>0.4375</v>
       </c>
       <c r="O18" t="n">
-        <v>0.125</v>
+        <v>0.107</v>
       </c>
       <c r="P18" t="n">
-        <v>1.2755</v>
+        <v>1.1773</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.4715</v>
+        <v>0.386</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1299</v>
+        <v>0.1114</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1851</v>
+        <v>0.1546</v>
       </c>
       <c r="T18" t="n">
         <v>60</v>
@@ -2952,43 +2952,43 @@
         <v>37</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0625</v>
+        <v>0.875</v>
       </c>
       <c r="W18" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>1.5905</v>
+        <v>1.4433</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.04511</v>
+        <v>0.03866</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.02083</v>
+        <v>0.01786</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.08333</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.72</v>
+        <v>0.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>0.96</v>
+        <v>0.945</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.96</v>
+        <v>1.775</v>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>2706-12-12</t>
+          <t>2706-08-10-LN</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 3/4-14 NPTF x 1 1/16-12 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 7/8-14 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
@@ -2998,39 +2998,39 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>3/4-14 NPTF</t>
+          <t>1/2-14 NPTF</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1 1/16-12 (bulkhead)</t>
+          <t>7/8-14 (bulkhead)</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1093 Overall Length = 2.800 (table had 2.72); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1093 Side 1 ID = 0.484 (table had 0.53) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 2.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.8) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 0.53 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.484) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L25@DRIVE=2.92~2.920; C2HEX@HEX=1.38~1.375; D1@BORE=0.72~0.719; D@BORE=0.61~0.609</t>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 2.8 -&gt; Air-Way 2.72 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 0.484 -&gt; Air-Way 0.53</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2706-12-12</t>
+          <t>2706-LN-08-10</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2706-12-12-LN</t>
+          <t>2706-12-12</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -3125,12 +3125,12 @@
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>2706-12-12-LN</t>
+          <t>2706-12-12</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 3/4-14 NPTF x 1 1/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 3/4-14 NPTF x 1 1/16-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
@@ -3165,54 +3165,54 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2706-LN-12-12</t>
+          <t>2706-12-12</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2706-16-16</t>
+          <t>2706-12-12-LN</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.11</v>
+        <v>2.92</v>
       </c>
       <c r="C20" t="n">
-        <v>0.94108</v>
+        <v>0.79674</v>
       </c>
       <c r="D20" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="G20" t="n">
         <v>1.7899</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2572</v>
+        <v>0.2043</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2832</v>
+        <v>1.02482</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6828</v>
+        <v>0.5457</v>
       </c>
       <c r="K20" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.51241</v>
       </c>
       <c r="M20" t="n">
-        <v>0.57203</v>
+        <v>0.45527</v>
       </c>
       <c r="N20" t="n">
-        <v>0.65625</v>
+        <v>0.53125</v>
       </c>
       <c r="O20" t="n">
         <v>0.125</v>
@@ -3221,13 +3221,13 @@
         <v>1.2755</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5965</v>
+        <v>0.4715</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1292</v>
+        <v>0.1299</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1858</v>
+        <v>0.1851</v>
       </c>
       <c r="T20" t="n">
         <v>60</v>
@@ -3236,7 +3236,7 @@
         <v>37</v>
       </c>
       <c r="V20" t="n">
-        <v>1.3125</v>
+        <v>1.0625</v>
       </c>
       <c r="W20" t="n">
         <v>0.08333</v>
@@ -3254,25 +3254,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.15</v>
+        <v>0.96</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="AE20" t="n">
         <v>1.96</v>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>2706-16-16</t>
+          <t>2706-12-12-LN</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1-11 1/2 NPTF x 1 5/16-12 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 3/4-14 NPTF x 1 1/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
@@ -3282,39 +3282,39 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1-11 1/2 NPTF</t>
+          <t>3/4-14 NPTF</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>1 5/16-12 (bulkhead)</t>
+          <t>1 1/16-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1080 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.17 -&gt; Air-Way 3.11</t>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L25@DRIVE=2.92~2.920; C2HEX@HEX=1.38~1.375; D1@BORE=0.72~0.719; D@BORE=0.61~0.609</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2706-16-16</t>
+          <t>2706-LN-12-12</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2706-16-16-LN</t>
+          <t>2706-16-16</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -3409,12 +3409,12 @@
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>2706-16-16-LN</t>
+          <t>2706-16-16</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1-11 1/2 NPTF x 1 5/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1-11 1/2 NPTF x 1 5/16-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1095 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1080 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -3449,69 +3449,69 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2706-LN-16-16</t>
+          <t>2706-16-16</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2706-20-20</t>
+          <t>2706-16-16-LN</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="C22" t="n">
-        <v>1.08542</v>
+        <v>0.94108</v>
       </c>
       <c r="D22" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="E22" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="G22" t="n">
         <v>1.7899</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2632</v>
+        <v>0.2572</v>
       </c>
       <c r="I22" t="n">
-        <v>1.6267</v>
+        <v>1.2832</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7068</v>
+        <v>0.6828</v>
       </c>
       <c r="K22" t="n">
         <v>0.08696</v>
       </c>
       <c r="L22" t="n">
-        <v>0.81335</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>0.74378</v>
+        <v>0.57203</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8125</v>
+        <v>0.65625</v>
       </c>
       <c r="O22" t="n">
         <v>0.125</v>
       </c>
       <c r="P22" t="n">
-        <v>1.2736</v>
+        <v>1.2755</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.753</v>
+        <v>0.5965</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1288</v>
+        <v>0.1292</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2382</v>
+        <v>0.1858</v>
       </c>
       <c r="T22" t="n">
         <v>60</v>
@@ -3520,13 +3520,13 @@
         <v>37</v>
       </c>
       <c r="V22" t="n">
-        <v>1.625</v>
+        <v>1.3125</v>
       </c>
       <c r="W22" t="n">
         <v>0.08333</v>
       </c>
       <c r="X22" t="n">
-        <v>1.6406</v>
+        <v>1.5905</v>
       </c>
       <c r="Y22" t="n">
         <v>0.04511</v>
@@ -3538,25 +3538,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.25</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>2706-20-20</t>
+          <t>2706-16-16-LN</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1 1/4-11 1/2 NPTF x 1 5/8-12 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1-11 1/2 NPTF x 1 5/16-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1 1/4-11 1/2 NPTF</t>
+          <t>1-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>1 5/8-12 (bulkhead)</t>
+          <t>1 5/16-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -3581,24 +3581,24 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1081 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.32) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1095 Overall Length = 3.170 (table had 3.11) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.11 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.17) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.32 -&gt; Air-Way 3.25</t>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.17 -&gt; Air-Way 3.11</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2706-20-20</t>
+          <t>2706-LN-16-16</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2706-20-20-LN</t>
+          <t>2706-20-20</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>2706-20-20-LN</t>
+          <t>2706-20-20</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1 1/4-11 1/2 NPTF x 1 5/8-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1 1/4-11 1/2 NPTF x 1 5/8-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1096 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.32) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1081 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.32) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -3733,69 +3733,69 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2706-LN-20-20</t>
+          <t>2706-20-20</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2706-24-24</t>
+          <t>2706-20-20-LN</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="C24" t="n">
-        <v>1.22976</v>
+        <v>1.08542</v>
       </c>
       <c r="D24" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="E24" t="n">
-        <v>0.93283</v>
+        <v>0.81335</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7235</v>
+        <v>0.7068</v>
       </c>
       <c r="G24" t="n">
         <v>1.7899</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2765</v>
+        <v>0.2632</v>
       </c>
       <c r="I24" t="n">
-        <v>1.86566</v>
+        <v>1.6267</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7235</v>
+        <v>0.7068</v>
       </c>
       <c r="K24" t="n">
         <v>0.08696</v>
       </c>
       <c r="L24" t="n">
-        <v>0.93283</v>
+        <v>0.81335</v>
       </c>
       <c r="M24" t="n">
-        <v>0.86326</v>
+        <v>0.74378</v>
       </c>
       <c r="N24" t="n">
-        <v>0.9375</v>
+        <v>0.8125</v>
       </c>
       <c r="O24" t="n">
         <v>0.125</v>
       </c>
       <c r="P24" t="n">
-        <v>1.2724</v>
+        <v>1.2736</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.753</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1298</v>
+        <v>0.1288</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2482</v>
+        <v>0.2382</v>
       </c>
       <c r="T24" t="n">
         <v>60</v>
@@ -3804,13 +3804,13 @@
         <v>37</v>
       </c>
       <c r="V24" t="n">
-        <v>1.875</v>
+        <v>1.625</v>
       </c>
       <c r="W24" t="n">
         <v>0.08333</v>
       </c>
       <c r="X24" t="n">
-        <v>1.6504</v>
+        <v>1.6406</v>
       </c>
       <c r="Y24" t="n">
         <v>0.04511</v>
@@ -3822,25 +3822,25 @@
         <v>0.08333</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.315</v>
+        <v>1.21</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.31</v>
+        <v>1.08</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.125</v>
+        <v>2.04</v>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>2706-24-24</t>
+          <t>2706-20-20-LN</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1 1/2-11 1/2 NPTF x 1 7/8-12 (bulkhead)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1 1/4-11 1/2 NPTF x 1 5/8-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
         </is>
       </c>
       <c r="AH24" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>1 1/2-11 1/2 NPTF</t>
+          <t>1 1/4-11 1/2 NPTF</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>1 7/8-12 (bulkhead)</t>
+          <t>1 5/8-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -3865,24 +3865,24 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1082 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1082 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.44 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 1.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.312) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1096 Overall Length = 3.320 (table had 3.25) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.25 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.32) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.5 -&gt; Air-Way 3.44 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 1.312 -&gt; Air-Way 1.5</t>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.32 -&gt; Air-Way 3.25</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2706-24-24</t>
+          <t>2706-LN-20-20</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2706-24-24-LN</t>
+          <t>2706-24-24</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>2706-24-24-LN</t>
+          <t>2706-24-24</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>Male Pipe x JIC Bulkhead Connector, 1 1/2-11 1/2 NPTF x 1 7/8-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+          <t>Male Pipe x JIC Bulkhead Connector, 1 1/2-11 1/2 NPTF x 1 7/8-12 (bulkhead)</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -4007,79 +4007,79 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1097 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1097 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; THDMAJ_A@DRIVE: 1.900 = ASME B1.20.1 1-1/2 NPT OD (ms51500.NPTF[24]) for the part-number dash -24 (table had empty: Air-Way callout "1 1/2-11" = nominal 1 1/2 with a TPI misprint); OMi Items!U1097 "1 1/2-11 1/2 NPFT" and Brennan TFA p9 "1-1/2-11-1/2" agree [thread size from the OMi dimension file's own thread cell Items!U1097 (OMi first, user 2026-09-25), not a dash transfer; Q18 / Q-THREAD not needed (impact F45D) - single source, ASSUMED] [batch 15 2026-10-02, staged]; L25@DRIVE: Air-Way 3.44 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 1.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.312) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1082 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1082 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L25@DRIVE: Air-Way 3.44 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 1.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.312) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>A NPTF printed "1 1/2-11" on Air-Way (sibling 1 1/2-11 1/2); copied as printed in $PRP@Threads - as-printed, likely typo | RESOLVED 2026-10-02 (batch 15, staged): THDMAJ_A = 1.900, the 1-1/2 NPT of the part-number dash -24 (ASME B1.20.1); OMi Items!U1097 prints "1 1/2-11 1/2 NPFT" and Brennan TFA p9 2706-24-24 prints "1-1/2-11-1/2"; the OMi thread cell is the source (no dash transfer, Q-THREAD not needed per impact F45D) - ASSUMED | 2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.5 -&gt; Air-Way 3.44 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 1.312 -&gt; Air-Way 1.5</t>
+          <t>2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.5 -&gt; Air-Way 3.44 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 1.312 -&gt; Air-Way 1.5</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2706-LN-24-24</t>
+          <t>2706-24-24</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2706-LN-04-02</t>
+          <t>2706-24-24-LN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.98</v>
+        <v>3.44</v>
       </c>
       <c r="C26" t="n">
-        <v>0.36084</v>
+        <v>1.22976</v>
       </c>
       <c r="D26" t="n">
-        <v>0.625</v>
+        <v>2.13</v>
       </c>
       <c r="E26" t="n">
-        <v>0.26092</v>
+        <v>0.93283</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4018</v>
+        <v>0.7235</v>
       </c>
       <c r="G26" t="n">
         <v>1.7899</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1582</v>
+        <v>0.2765</v>
       </c>
       <c r="I26" t="n">
-        <v>0.52183</v>
+        <v>1.86566</v>
       </c>
       <c r="J26" t="n">
-        <v>0.4018</v>
+        <v>0.7235</v>
       </c>
       <c r="K26" t="n">
-        <v>0.05556</v>
+        <v>0.08696</v>
       </c>
       <c r="L26" t="n">
-        <v>0.26092</v>
+        <v>0.93283</v>
       </c>
       <c r="M26" t="n">
-        <v>0.21647</v>
+        <v>0.86326</v>
       </c>
       <c r="N26" t="n">
-        <v>0.15625</v>
+        <v>0.9375</v>
       </c>
       <c r="O26" t="n">
-        <v>0.063</v>
+        <v>0.125</v>
       </c>
       <c r="P26" t="n">
-        <v>0.852</v>
+        <v>1.2724</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.125</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="R26" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.1298</v>
       </c>
       <c r="S26" t="n">
-        <v>0.1108</v>
+        <v>0.2482</v>
       </c>
       <c r="T26" t="n">
         <v>60</v>
@@ -4088,78 +4088,646 @@
         <v>37</v>
       </c>
       <c r="V26" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.6504</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.315</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>2706-24-24-LN</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Male Pipe x JIC Bulkhead Connector, 1 1/2-11 1/2 NPTF x 1 7/8-12 (bulkhead) (with bulkhead locknut - locknut not modelled)</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>1 1/2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>1 7/8-12 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AL26" t="inlineStr">
+        <is>
+          <t>Air-Way s74 only (double-pass 25 rows); L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1097 Overall Length = 3.500 (table had 3.44); D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1097 Side 1 ID = 1.312 (table had 1.5) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; THDMAJ_A@DRIVE: 1.900 = ASME B1.20.1 1-1/2 NPT OD (ms51500.NPTF[24]) for the part-number dash -24 (table had empty: Air-Way callout "1 1/2-11" = nominal 1 1/2 with a TPI misprint); OMi Items!U1097 "1 1/2-11 1/2 NPFT" and Brennan TFA p9 "1-1/2-11-1/2" agree [thread size from the OMi dimension file's own thread cell Items!U1097 (OMi first, user 2026-09-25), not a dash transfer; Q18 / Q-THREAD not needed (impact F45D) - single source, ASSUMED] [batch 15 2026-10-02, staged]; L25@DRIVE: Air-Way 3.44 (raw 07_RAW_EXTRACTS; OMi file / Brennan 3.5) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; D1@BORE: Air-Way 1.5 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.312) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)] | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>A NPTF printed "1 1/2-11" on Air-Way (sibling 1 1/2-11 1/2); copied as printed in $PRP@Threads - as-printed, likely typo | RESOLVED 2026-10-02 (batch 15, staged): THDMAJ_A = 1.900, the 1-1/2 NPT of the part-number dash -24 (ASME B1.20.1); OMi Items!U1097 prints "1 1/2-11 1/2 NPFT" and Brennan TFA p9 2706-24-24 prints "1-1/2-11-1/2"; the OMi thread cell is the source (no dash transfer, Q-THREAD not needed per impact F45D) - ASSUMED | 2026-10-20 Air-Way first: L25@DRIVE OMi/Brennan 3.5 -&gt; Air-Way 3.44 | 2026-10-20 Air-Way first: D1@BORE OMi/Brennan 1.312 -&gt; Air-Way 1.5</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>2706-LN-24-24</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2706-32-32</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.58771</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.2735</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2.33859</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.7565</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.16929</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.09973</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.4694</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="T27" t="n">
+        <v>60</v>
+      </c>
+      <c r="U27" t="n">
+        <v>37</v>
+      </c>
+      <c r="V27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.9304</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.02083</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.938</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.425</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.781</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.485</v>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>2706-32-32</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Male Pipe x JIC Bulkhead Connector, 2-11 1/2 NPTF x 2 1/2-12 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>2-11 1/2 NPTF</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>2 1/2-12 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AL27" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L25 / hex / D1 / D = OMi WebsitePartsInfo2026.xlsx Items row 1083; I1 2.09 = Air-Way -32 bulkhead (A8); thread majors from the end library; cross-check Brennan TFA p9 2706-32-32: L 3.91, C1 HEX 2.750, A1 DRILL 1.938, B2 DRILL 1.781 - all equal (same manufacturer, one source) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 1083 + A8 I1 per size; cross-check Brennan TFA p9 2706-32-32: L 3.91, C1 HEX 2.750, A1 DRILL 1.938, B2 DRILL 1.781 - all equal (same manufacturer, one source)</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>2706-32-32</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2706-LN-04-02</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1582</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.52183</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.21647</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.852</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.06619999999999999</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.1108</v>
+      </c>
+      <c r="T28" t="n">
+        <v>60</v>
+      </c>
+      <c r="U28" t="n">
+        <v>37</v>
+      </c>
+      <c r="V28" t="n">
         <v>0.3125</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W28" t="n">
         <v>0.04167</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X28" t="n">
         <v>1.029</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Y28" t="n">
         <v>0.02255</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="Z28" t="n">
         <v>0.01042</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AA28" t="n">
         <v>0.04167</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AB28" t="n">
         <v>0.281</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AC28" t="n">
         <v>0.715</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AD28" t="n">
         <v>0.062</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AE28" t="n">
         <v>1.265</v>
       </c>
-      <c r="AF26" t="inlineStr">
+      <c r="AF28" t="inlineStr">
         <is>
           <t>2706-LN-04-02</t>
         </is>
       </c>
-      <c r="AG26" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>Male Pipe x JIC Bulkhead Connector, 1/4-18 NPTF x 5/16-24 (bulkhead)</t>
         </is>
       </c>
-      <c r="AH26" t="inlineStr">
+      <c r="AH28" t="inlineStr">
         <is>
           <t>2706</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
+      <c r="AI28" t="inlineStr">
         <is>
           <t>1/4-18 NPTF</t>
         </is>
       </c>
-      <c r="AJ26" t="inlineStr">
+      <c r="AJ28" t="inlineStr">
         <is>
           <t>5/16-24 (bulkhead)</t>
         </is>
       </c>
-      <c r="AK26" t="inlineStr">
+      <c r="AK28" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="AL26" t="inlineStr">
+      <c r="AL28" t="inlineStr">
         <is>
           <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L25@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1085 "Overall Length" = 1.980 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "L LGTH" = "1.980" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; C2HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1085 "Hex Flat" = 0.625 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "C1 HEX" = "0.625" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1085 "Side 1 ID" = 0.281 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "A1 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; D@BORE: OMi WebsitePartsInfo2026.xlsx Items!X1085 "Side 2 ID" = 0.062 (OMi first, user 2026-09-25; mapping impact/F2a.json M059-M062 certain); cross-check Brennan TFA catalog p9 table TFA-p009-t01 "2706 MP-MJ BULKHEAD STRAIGHT" row 2706-04-02 col "B2 DRILL" = "0.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; brennan_catalog_20261001/catalog_verified.json, line_y 156.2, page verified): equal; I1@DRIVE: own Brennan STEP 09_STEP_FILES/BRENNAN_2706-04-02.stp (sha256 d4ff2da4fb37563b...) measured with wave2/straight/scripts/measure_bulkhead.py (validated on Brennan 2705-08-08 = Air-Way I1 1.44): bulkhead tip 1.42 - relief start 0.31 = 1.11; STEP overall 1.98 = OMi / catalog 1.980, hex 0.6251 = 0.625 [Brennan = yes 2026-10-18] [the -LN part = the plain 2706-04-02 + a locknut: Q-TRANSFER-LN open]; THDMAJ_A@DRIVE: end library: ASME B1.20.1 / B1.20.3 1/4 NPT basic dimensions = tools_new/generators/ms51500.NPTF[4] [Q-TRANSFER-ENDLIB yes 2026-10-08] pipe OD; OMi Items!U1085 "1/4-18 NPTF"; THDMAJ_B@DRIVE: end library gen_straight2 JIC[2] (= tools_new/generators/templates/DesignTable_2403_SW2.xlsx, MS33656J chain, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08] thread major; OMi Items!AA1085 "5/16-24 UNF"; $PRP@TubeOD: Brennan TFA p9 TFA-p009-t01 row 2706-04-02 col "TUBE O.D." = "1/8" (= the -02 JIC tube; format of the built 2706 rows); $PRP@Threads: thread texts from the part-number dashes (NPTF[4] / JIC[2]), format of the built 2706 rows | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
+      <c r="AM28" t="inlineStr">
         <is>
           <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave 2 straight, staged, not shipped): L25 / hex / bores from OMi Items (= Brennan TFA p9); I1 measured on the Brennan 2706-04-02 STEP (no Air-Way -02 bulkhead) - copied from the plain part (Q-TRANSFER-LN)</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
+      <c r="AN28" t="inlineStr">
         <is>
           <t>2706-LN-04-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2706-LN-06-04</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.43301</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1522</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.65645</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.28378</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.9108000000000001</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.0795</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.1135</v>
+      </c>
+      <c r="T29" t="n">
+        <v>60</v>
+      </c>
+      <c r="U29" t="n">
+        <v>37</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.1038</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0.02706</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.415</v>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>2706-LN-06-04</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Male Pipe x JIC Bulkhead Connector, 3/8-18 NPTF x 7/16-20 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>3/8-18 NPTF</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>7/16-20 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): L25 / hex / D1 / D = OMi WebsitePartsInfo2026.xlsx Items row 1088; I1 1.20 = Air-Way -04 bulkhead (A8); -LN modelled as the plain part, no locknut (A10); thread majors from the end library; own -LN row = the plain 2706-06-04 (Items row 1073); not printed in the Brennan TFA catalog | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): filled from OMi Items row 1088 + A8 I1 per size + A10; own -LN row = the plain 2706-06-04 (Items row 1073); not printed in the Brennan TFA catalog</t>
+        </is>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>2706-LN-06-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2706-LN-08-06</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.50807</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.7899</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2163</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.81557</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5337</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.40779</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.9755</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.2405</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.0898</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.1082</v>
+      </c>
+      <c r="T30" t="n">
+        <v>60</v>
+      </c>
+      <c r="U30" t="n">
+        <v>37</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.1735</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0.03007</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.05556</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.435</v>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>2706-LN-08-06</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>Male Pipe x JIC Bulkhead Connector, 1/2-14 NPTF x 9/16-18 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>2706</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>9/16-18 (bulkhead)</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-20 batch-19 stage A_answered (not shipped): every size = the plain twin 2706-08-06 = Air-Way 2706.csv line 12 (2706-8-6, the plain twin; = the live review row 2706-08-06) (A10: -LN modelled as the plain part, no locknut; Air-Way first 2026-10-20); OMi own -LN row (Items row 1091) L 2.400 / hex 0.875 / D1 0.531 / D 0.295 and Brennan TFA p9 2706-08-06 L 2.410 / B2 DRILL 0.297 not used (Air-Way prints the part) | MODEL: male NPTF end per ASME B1.20.3 with the 5404 Brennan-measured end length for the same dash (ASSUMPTION); JIC bulkhead end: MS33656J nose chain per dash (seat, land, relief, 60deg ramp; 2403 table, VERIFIED vs Brennan) with the JIC thread extended over the full bulkhead length I1 (Air-Way) - construction confirmed on the Brennan 2705-08-08 STEP (thread 0.750-16 from the relief to the land; Brennan I1 from the relief 1.44 = Air-Way); the Brennan 0.04 collar at the hex face and its 0.679 relief (vs the 0.659 cone dia used here) are NOT modelled; -LN configs = the same fitting shipped with a bulkhead locknut (separate part 0306, not modelled); bore step (D1 pipe side / D bulkhead side) at the hex mid-plane (ASSUMPTION)</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-20 batch-19 stage A_answered (not shipped): = the plain 2706-08-06 (A10); OMi -LN row L 2.400 / D 0.295 and Brennan L 2.410 differ from Air-Way (2.34 / 0.30) - Air-Way first (2026-10-20), as on the plain twin</t>
+        </is>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>2706-LN-08-06</t>
         </is>
       </c>
     </row>
